--- a/downloads/Fictional_Sales_Activity_Tracker.xlsx
+++ b/downloads/Fictional_Sales_Activity_Tracker.xlsx
@@ -2,41 +2,41 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rff140e2c3da4412c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Summary" sheetId="2" r:id="R1f8db16775184c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" r:id="R944060f4550c4a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 01" sheetId="4" r:id="R66cf28a72a36497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 02" sheetId="5" r:id="R83cb4c9ca7ae475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 03" sheetId="6" r:id="Rb17ec90ffa0f44fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 04" sheetId="7" r:id="Rf8e57e36a5db421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 05" sheetId="8" r:id="Rf14997c049124f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 06" sheetId="9" r:id="R080bc3883d1749d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 07" sheetId="10" r:id="R18db0de3a03b408d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 08" sheetId="11" r:id="R916a9a69939d495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 09" sheetId="12" r:id="Rea712376ad23404a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 10" sheetId="13" r:id="R0d974abcf55d4f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 11" sheetId="14" r:id="R5d78a7734e114d1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 12" sheetId="15" r:id="Rf0a13ef6f94142b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 13" sheetId="16" r:id="Ra8964810f0c7499b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 14" sheetId="17" r:id="R1a6ecbcec2cf4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 15" sheetId="18" r:id="R8bbe0dabd07348fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 16" sheetId="19" r:id="R726ffa8159db48e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 17" sheetId="20" r:id="Rd2d6da010a474540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 18" sheetId="21" r:id="R6799dab5ae6d4121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 19" sheetId="22" r:id="R536fe4c3d96a4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 20" sheetId="23" r:id="R615cf9fe27d04f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 21" sheetId="24" r:id="Rf3e69b04499c4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 22" sheetId="25" r:id="Ra3822329732845ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 23" sheetId="26" r:id="R3712f0338f604e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 24" sheetId="27" r:id="R8d8ec8e4cf8c4fff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 25" sheetId="28" r:id="R7df446cb551a46fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 26" sheetId="29" r:id="R2c153c8328ed40bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 27" sheetId="30" r:id="R188c215b48f0463c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 28" sheetId="31" r:id="Rbe5100b3e0df4311"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 29" sheetId="32" r:id="Radaf715a01c5413b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 30" sheetId="33" r:id="Rf67a557774f247ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 31" sheetId="34" r:id="R3ac9cde5e826462c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="35" r:id="R90405f43c66e467a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7f7f6010f77d44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Summary" sheetId="2" r:id="R05570557194d4f48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="3" r:id="Ree46dfb23008415d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 01" sheetId="4" r:id="Rc51105309826405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 02" sheetId="5" r:id="R807c340f95b44492"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 03" sheetId="6" r:id="Rc0f3d56c5b804706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 04" sheetId="7" r:id="Rf4186e1e53724985"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 05" sheetId="8" r:id="R86e98258366e4d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 06" sheetId="9" r:id="R8d2fa77179234bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 07" sheetId="10" r:id="R8bb22eca0cbb4bd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 08" sheetId="11" r:id="R7d72b275a0184713"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 09" sheetId="12" r:id="R5f4341cd007841db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 10" sheetId="13" r:id="R4bfe182f221049ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 11" sheetId="14" r:id="R2a1303a648e54bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 12" sheetId="15" r:id="R39c8a39f00d941bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 13" sheetId="16" r:id="R62221f54a9394c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 14" sheetId="17" r:id="Ra0d3bd25a3234e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 15" sheetId="18" r:id="Ra75eec7f014c4b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 16" sheetId="19" r:id="Rfd89852bca36478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 17" sheetId="20" r:id="R929a5b40ed2f4752"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 18" sheetId="21" r:id="R1a44cae787314ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 19" sheetId="22" r:id="R3974a023634e482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 20" sheetId="23" r:id="R441648c632904d16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 21" sheetId="24" r:id="R584f2767befe4295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 22" sheetId="25" r:id="Rc7842cbce6d04032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 23" sheetId="26" r:id="R6e4fe66008c44233"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 24" sheetId="27" r:id="Ra7322e31d63c43b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 25" sheetId="28" r:id="Rc3cb782dcd7b447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 26" sheetId="29" r:id="R07853c6c92a44b18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 27" sheetId="30" r:id="Rac8100084914490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 28" sheetId="31" r:id="R3c196228381646a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 29" sheetId="32" r:id="Rac345fda538643d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 30" sheetId="33" r:id="R8b069fda5006493b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Day 31" sheetId="34" r:id="R0a1c44475ac54e58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="35" r:id="R29b41569164645dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,7 +88,7 @@
     <x:numFmt numFmtId="206" formatCode="0%"/>
     <x:numFmt numFmtId="207" formatCode="mmm d"/>
   </x:numFmts>
-  <x:fonts count="20">
+  <x:fonts count="22">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -202,6 +202,17 @@
       <x:sz val="11"/>
       <x:color rgb="FF7C4A03"/>
       <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF0B1F33"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF0B1F33"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="12">
@@ -504,7 +515,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="542">
+  <x:cellXfs count="546">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1627,6 +1638,14 @@
     <x:xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1638,7 +1657,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1649,7 +1668,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1659,7 +1678,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1669,7 +1688,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1680,7 +1699,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -1691,7 +1710,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1701,7 +1720,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1712,7 +1731,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1723,7 +1742,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1733,7 +1752,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1743,7 +1762,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1754,7 +1773,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -1765,7 +1784,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1775,7 +1794,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1786,7 +1805,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1797,7 +1816,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1807,7 +1826,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1817,7 +1836,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1828,7 +1847,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -1839,7 +1858,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1849,7 +1868,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1860,7 +1879,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1871,7 +1890,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1881,7 +1900,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1891,7 +1910,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1902,7 +1921,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -1913,7 +1932,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1923,7 +1942,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -1934,7 +1953,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1945,7 +1964,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1955,7 +1974,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1965,7 +1984,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -1976,7 +1995,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -1987,7 +2006,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -1997,7 +2016,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2008,7 +2027,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2019,7 +2038,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2029,7 +2048,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2039,7 +2058,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2050,7 +2069,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2061,7 +2080,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2071,7 +2090,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2082,7 +2101,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2093,7 +2112,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2103,7 +2122,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2113,7 +2132,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2124,7 +2143,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2135,7 +2154,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2145,7 +2164,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2156,7 +2175,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2167,7 +2186,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2177,7 +2196,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2187,7 +2206,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2198,7 +2217,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2209,7 +2228,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2219,7 +2238,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2230,7 +2249,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2241,7 +2260,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2251,7 +2270,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2261,7 +2280,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2272,7 +2291,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2283,7 +2302,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2293,7 +2312,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2304,7 +2323,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2315,7 +2334,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2325,7 +2344,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2335,7 +2354,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2346,7 +2365,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2357,7 +2376,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2367,7 +2386,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2378,7 +2397,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2389,7 +2408,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2399,7 +2418,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2409,7 +2428,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2420,7 +2439,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2431,7 +2450,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2441,7 +2460,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2452,7 +2471,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2463,7 +2482,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2473,7 +2492,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2483,7 +2502,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2494,7 +2513,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2505,7 +2524,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2515,7 +2534,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2526,7 +2545,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2537,7 +2556,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2547,7 +2566,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2557,7 +2576,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2568,7 +2587,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2579,7 +2598,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2589,7 +2608,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2600,7 +2619,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2611,7 +2630,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2621,7 +2640,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2631,7 +2650,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2642,7 +2661,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2653,7 +2672,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2663,7 +2682,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2674,7 +2693,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2685,7 +2704,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2695,7 +2714,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2705,7 +2724,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2716,7 +2735,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2727,7 +2746,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2737,7 +2756,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2748,7 +2767,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2759,7 +2778,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2769,7 +2788,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2779,7 +2798,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2790,7 +2809,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2801,7 +2820,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2811,7 +2830,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2822,7 +2841,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2833,7 +2852,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2843,7 +2862,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2853,7 +2872,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2864,7 +2883,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2875,7 +2894,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2885,7 +2904,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2896,7 +2915,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2907,7 +2926,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2917,7 +2936,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2927,7 +2946,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2938,7 +2957,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -2949,7 +2968,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2959,7 +2978,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -2970,7 +2989,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -2981,7 +3000,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -2991,7 +3010,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3001,7 +3020,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3012,7 +3031,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3023,7 +3042,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3033,7 +3052,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3044,7 +3063,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3055,7 +3074,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3065,7 +3084,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3075,7 +3094,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3086,7 +3105,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3097,7 +3116,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3107,7 +3126,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3118,7 +3137,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3129,7 +3148,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3139,7 +3158,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3149,7 +3168,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3160,7 +3179,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3171,7 +3190,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3181,7 +3200,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3192,7 +3211,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3203,7 +3222,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3213,7 +3232,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3223,7 +3242,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3234,7 +3253,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3245,7 +3264,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3255,7 +3274,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3266,7 +3285,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3277,7 +3296,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3287,7 +3306,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3297,7 +3316,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3308,7 +3327,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3319,7 +3338,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3329,7 +3348,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3340,7 +3359,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3351,7 +3370,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3361,7 +3380,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3371,7 +3390,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3382,7 +3401,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3393,7 +3412,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3403,7 +3422,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3414,7 +3433,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3425,7 +3444,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3435,7 +3454,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3445,7 +3464,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3456,7 +3475,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3467,7 +3486,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3477,7 +3496,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3488,7 +3507,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3499,7 +3518,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3509,7 +3528,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3519,7 +3538,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3530,7 +3549,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3541,7 +3560,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3551,7 +3570,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3562,7 +3581,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3573,7 +3592,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3583,7 +3602,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3593,7 +3612,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3604,7 +3623,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3615,7 +3634,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3625,7 +3644,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3636,7 +3655,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3647,7 +3666,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3657,7 +3676,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3667,7 +3686,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3678,7 +3697,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3689,7 +3708,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3699,7 +3718,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3710,7 +3729,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3721,7 +3740,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3731,7 +3750,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3741,7 +3760,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3752,7 +3771,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3763,7 +3782,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3773,7 +3792,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3784,7 +3803,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3795,7 +3814,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3805,7 +3824,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3815,7 +3834,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3826,7 +3845,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3837,7 +3856,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3847,7 +3866,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3858,7 +3877,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3869,7 +3888,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3879,7 +3898,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3889,7 +3908,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -3900,7 +3919,7 @@
         <x:color rgb="FF315EEA"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE9EDFA"/>
         </x:patternFill>
       </x:fill>
@@ -3911,7 +3930,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3921,7 +3940,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -3932,7 +3951,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -3942,7 +3961,7 @@
         <x:color rgb="FF92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE68A"/>
         </x:patternFill>
       </x:fill>
@@ -4282,7 +4301,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R278e9b45766048d5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a92e1f2f4b44247"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4312,7 +4331,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0523cfec67c14d1e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0c96e1b6011a46d3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -5813,7 +5832,7 @@
     <x:mergeCell ref="L28:N32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R476d0d110a2740d7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e7febd4e7744a2b"/>
 </x:worksheet>
 </file>
 
@@ -6030,7 +6049,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -6074,7 +6093,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -6118,7 +6137,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -6161,7 +6180,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -6204,7 +6223,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -6232,7 +6251,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -6260,7 +6279,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -6295,7 +6314,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -6329,7 +6348,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -6363,7 +6382,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -6398,7 +6417,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -6433,7 +6452,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -6590,7 +6609,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cb08a4a9ad64f1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bbfaf2538064071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6808,7 +6827,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -6851,7 +6870,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -6894,7 +6913,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -6938,7 +6957,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -6982,7 +7001,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -7010,7 +7029,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -7071,7 +7090,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -7106,7 +7125,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -7141,7 +7160,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -7176,7 +7195,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -7210,7 +7229,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -7237,7 +7256,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -7265,7 +7284,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -7293,7 +7312,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -7321,7 +7340,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -7348,7 +7367,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -7445,7 +7464,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5095710641784ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb4d8b51e8cb421f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7662,7 +7681,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -7705,7 +7724,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -7749,7 +7768,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -7793,7 +7812,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -7837,7 +7856,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -7891,7 +7910,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -7926,7 +7945,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -7961,7 +7980,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -7996,7 +8015,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -8030,7 +8049,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -8064,7 +8083,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -8092,7 +8111,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -8120,7 +8139,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -8148,7 +8167,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -8269,7 +8288,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra18e078552d3487e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc80cbd47f676421b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8487,7 +8506,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -8531,7 +8550,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -8575,7 +8594,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -8618,7 +8637,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -8661,7 +8680,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -8689,7 +8708,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -8717,7 +8736,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -8752,7 +8771,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -8786,7 +8805,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -8820,7 +8839,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -8855,7 +8874,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -8890,7 +8909,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -8918,7 +8937,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -9063,7 +9082,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3e5ba2469bde4924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc865e0d9e0184a9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9281,7 +9300,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -9325,7 +9344,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -9368,7 +9387,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -9411,7 +9430,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -9455,7 +9474,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -9483,7 +9502,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -9511,7 +9530,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -9545,7 +9564,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -9579,7 +9598,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -9614,7 +9633,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -9649,7 +9668,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -9684,7 +9703,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -9711,7 +9730,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -9738,7 +9757,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -9766,7 +9785,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -9794,7 +9813,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -9822,7 +9841,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -9849,7 +9868,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H27" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
@@ -9934,7 +9953,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd786cbf4dd42e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7fdc56ba07499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10151,7 +10170,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -10194,7 +10213,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -10238,7 +10257,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -10282,7 +10301,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -10326,7 +10345,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -10353,7 +10372,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -10380,7 +10399,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -10415,7 +10434,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -10450,7 +10469,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -10485,7 +10504,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -10519,7 +10538,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -10553,7 +10572,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -10581,7 +10600,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -10609,7 +10628,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -10637,7 +10656,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -10664,7 +10683,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -10773,7 +10792,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe9427b215f4dfb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37c901e359a74142"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10990,7 +11009,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -11034,7 +11053,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -11078,7 +11097,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -11122,7 +11141,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -11165,7 +11184,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -11192,7 +11211,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -11220,7 +11239,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -11255,7 +11274,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -11290,7 +11309,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -11324,7 +11343,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -11358,7 +11377,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -11393,7 +11412,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -11421,7 +11440,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -11449,7 +11468,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -11582,7 +11601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82390953ad704f36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb5a9f375c314b4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11800,7 +11819,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -11844,7 +11863,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -11887,7 +11906,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -11930,7 +11949,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -11974,7 +11993,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -12002,7 +12021,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -12030,7 +12049,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -12064,7 +12083,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -12098,7 +12117,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -12133,7 +12152,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -12168,7 +12187,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -12203,7 +12222,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -12360,7 +12379,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R967486a48676433e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra725856dd4c4451c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12578,7 +12597,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -12621,7 +12640,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -12664,7 +12683,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -12708,7 +12727,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -12752,7 +12771,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -12780,7 +12799,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -12807,7 +12826,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -12841,7 +12860,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -12876,7 +12895,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -12911,7 +12930,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -12946,7 +12965,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -13007,7 +13026,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -13035,7 +13054,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -13063,7 +13082,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -13091,7 +13110,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -13118,7 +13137,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -13215,7 +13234,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ceb1f008c0d4971"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb4389c175f459e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13432,7 +13451,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -13476,7 +13495,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -13520,7 +13539,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -13564,7 +13583,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -13634,7 +13653,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -13662,7 +13681,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -13697,7 +13716,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -13732,7 +13751,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -13766,7 +13785,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -13800,7 +13819,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -13835,7 +13854,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -13863,7 +13882,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -13891,7 +13910,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -13918,7 +13937,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -14039,7 +14058,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14b35cecfd274bd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65738627ecb945ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15659,7 +15678,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47a08a24a1a14e1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b26b5a984954f8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15877,7 +15896,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -15921,7 +15940,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -15965,7 +15984,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -16051,7 +16070,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -16079,7 +16098,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -16107,7 +16126,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -16142,7 +16161,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -16176,7 +16195,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -16210,7 +16229,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -16245,7 +16264,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -16280,7 +16299,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -16308,7 +16327,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -16453,7 +16472,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4802f8ce3db34979"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3206e99f51564cf7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16671,7 +16690,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -16714,7 +16733,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -16757,7 +16776,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -16801,7 +16820,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -16845,7 +16864,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -16873,7 +16892,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -16900,7 +16919,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -16934,7 +16953,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -16969,7 +16988,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -17004,7 +17023,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -17039,7 +17058,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -17073,7 +17092,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -17100,7 +17119,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -17128,7 +17147,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -17156,7 +17175,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -17184,7 +17203,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -17211,7 +17230,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -17238,7 +17257,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H27" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
@@ -17323,7 +17342,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b6f67de768242cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R424be144a47e4a91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17540,7 +17559,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -17583,7 +17602,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -17627,7 +17646,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -17671,7 +17690,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -17715,7 +17734,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -17742,7 +17761,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -17769,7 +17788,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -17804,7 +17823,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -17839,7 +17858,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -17874,7 +17893,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -17908,7 +17927,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -17942,7 +17961,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -17970,7 +17989,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -17998,7 +18017,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -18026,7 +18045,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -18053,7 +18072,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -18162,7 +18181,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff743510b9664adc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9024a7982aa746f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18380,7 +18399,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -18424,7 +18443,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -18468,7 +18487,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -18511,7 +18530,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -18554,7 +18573,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -18582,7 +18601,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -18610,7 +18629,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -18645,7 +18664,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -18679,7 +18698,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -18713,7 +18732,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -18748,7 +18767,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -18783,7 +18802,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -18811,7 +18830,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -18838,7 +18857,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -18971,7 +18990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80a47ccf1fe648e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f78bcd77c14b7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19189,7 +19208,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -19233,7 +19252,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -19276,7 +19295,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -19319,7 +19338,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -19363,7 +19382,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -19391,7 +19410,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -19419,7 +19438,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -19453,7 +19472,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -19487,7 +19506,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -19522,7 +19541,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -19557,7 +19576,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -19592,7 +19611,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -19749,7 +19768,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c15b33fab5a4c00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce339db5661f4fac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19966,7 +19985,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -20009,7 +20028,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -20053,7 +20072,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -20097,7 +20116,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -20141,7 +20160,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -20168,7 +20187,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -20195,7 +20214,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -20230,7 +20249,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -20265,7 +20284,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -20300,7 +20319,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -20368,7 +20387,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -20396,7 +20415,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -20424,7 +20443,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -20452,7 +20471,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -20479,7 +20498,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -20506,7 +20525,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -20603,7 +20622,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47460a96aa8843c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee6b40fd7ae4b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20820,7 +20839,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -20864,7 +20883,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -20908,7 +20927,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -20952,7 +20971,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -20995,7 +21014,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -21022,7 +21041,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -21050,7 +21069,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -21085,7 +21104,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -21120,7 +21139,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -21188,7 +21207,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -21223,7 +21242,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -21251,7 +21270,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -21279,7 +21298,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -21306,7 +21325,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -21427,7 +21446,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e9633a33444e35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d61b9c3e9044a6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21645,7 +21664,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -21689,7 +21708,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -21775,7 +21794,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -21819,7 +21838,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -21847,7 +21866,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -21875,7 +21894,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -21909,7 +21928,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -21943,7 +21962,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -21978,7 +21997,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -22013,7 +22032,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -22048,7 +22067,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -22075,7 +22094,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -22220,7 +22239,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra27ffc8f9f6c4183"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R293f8f62a4614ca0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22438,7 +22457,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -22524,7 +22543,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -22568,7 +22587,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -22612,7 +22631,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -22640,7 +22659,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -22667,7 +22686,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -22701,7 +22720,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -22736,7 +22755,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -22771,7 +22790,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -22806,7 +22825,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -22840,7 +22859,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -22867,7 +22886,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -22895,7 +22914,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -22923,7 +22942,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -22951,7 +22970,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -22978,7 +22997,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -23005,7 +23024,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H27" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
@@ -23090,7 +23109,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1af97c384c184689"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R226e00eeb3534b85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23307,7 +23326,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -23351,7 +23370,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -23395,7 +23414,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -23439,7 +23458,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -23482,7 +23501,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -23509,7 +23528,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -23537,7 +23556,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -23572,7 +23591,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -23607,7 +23626,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -23641,7 +23660,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -23675,7 +23694,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -23710,7 +23729,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -23738,7 +23757,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -23766,7 +23785,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -23793,7 +23812,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -23820,7 +23839,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -23929,7 +23948,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b562a9315944f33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c7c967ed4214783"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24155,7 +24174,7 @@
     <x:mergeCell ref="F16:H16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66cd27e8331048a2"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dc59557e4e04710"/>
 </x:worksheet>
 </file>
 
@@ -24372,7 +24391,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -24416,7 +24435,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -24460,7 +24479,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -24503,7 +24522,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -24546,7 +24565,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -24574,7 +24593,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -24602,7 +24621,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -24637,7 +24656,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -24671,7 +24690,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -24705,7 +24724,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -24740,7 +24759,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -24775,7 +24794,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -24803,7 +24822,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -24830,7 +24849,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -24963,7 +24982,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd59fb01e3e04973"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20f1a72c6c7c464b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25181,7 +25200,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -25224,7 +25243,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -25267,7 +25286,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -25311,7 +25330,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -25355,7 +25374,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -25383,7 +25402,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -25410,7 +25429,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -25444,7 +25463,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -25479,7 +25498,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -25514,7 +25533,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -25549,7 +25568,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -25583,7 +25602,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -25740,7 +25759,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9905c2afee4451f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc47de5ac6d724aea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25957,7 +25976,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -26000,7 +26019,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -26044,7 +26063,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -26088,7 +26107,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -26132,7 +26151,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -26159,7 +26178,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -26186,7 +26205,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -26221,7 +26240,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -26256,7 +26275,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -26291,7 +26310,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -26325,7 +26344,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -26359,7 +26378,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -26387,7 +26406,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -26415,7 +26434,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -26443,7 +26462,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -26497,7 +26516,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -26594,7 +26613,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reaa3c7052a554114"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R15454b44ba4447f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26812,7 +26831,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -26856,7 +26875,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -26900,7 +26919,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -26943,7 +26962,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -26986,7 +27005,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -27014,7 +27033,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -27042,7 +27061,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -27077,7 +27096,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -27145,7 +27164,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -27180,7 +27199,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -27215,7 +27234,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -27243,7 +27262,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -27270,7 +27289,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -27297,7 +27316,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -27418,7 +27437,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdddc285294a4672"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb146f06f12e64469"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27636,7 +27655,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -27680,7 +27699,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -27723,7 +27742,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -27766,7 +27785,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -27810,7 +27829,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -27838,7 +27857,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -27866,7 +27885,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -27934,7 +27953,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -27969,7 +27988,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -28004,7 +28023,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -28039,7 +28058,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -28066,7 +28085,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -28211,7 +28230,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91635457bf2047d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec5c6f73dbad456d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28448,6 +28467,50 @@
       <x:c r="G25" s="541"/>
       <x:c r="H25" s="541"/>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="542" t="str">
+        <x:v>Two independent targets</x:v>
+      </x:c>
+      <x:c r="B27" s="542"/>
+      <x:c r="C27" s="542"/>
+      <x:c r="D27" s="542"/>
+      <x:c r="E27" s="542"/>
+      <x:c r="F27" s="542"/>
+      <x:c r="G27" s="542"/>
+      <x:c r="H27" s="542"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="545" t="str">
+        <x:v>Monthly product goals total 310 units. The separate daily target is 11 units, or 341 over 31 days. The 324 completed units equal 104.5% of product goals and 95.0% of the daily target summed across the month. Confirm the intended goals before interpreting this difference. All values are fictional.</x:v>
+      </x:c>
+      <x:c r="B28" s="545"/>
+      <x:c r="C28" s="545"/>
+      <x:c r="D28" s="545"/>
+      <x:c r="E28" s="545"/>
+      <x:c r="F28" s="545"/>
+      <x:c r="G28" s="545"/>
+      <x:c r="H28" s="545"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="545"/>
+      <x:c r="B29" s="545"/>
+      <x:c r="C29" s="545"/>
+      <x:c r="D29" s="545"/>
+      <x:c r="E29" s="545"/>
+      <x:c r="F29" s="545"/>
+      <x:c r="G29" s="545"/>
+      <x:c r="H29" s="545"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="545"/>
+      <x:c r="B30" s="545"/>
+      <x:c r="C30" s="545"/>
+      <x:c r="D30" s="545"/>
+      <x:c r="E30" s="545"/>
+      <x:c r="F30" s="545"/>
+      <x:c r="G30" s="545"/>
+      <x:c r="H30" s="545"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
@@ -28459,6 +28522,8 @@
     <x:mergeCell ref="A23:H23"/>
     <x:mergeCell ref="A24:H24"/>
     <x:mergeCell ref="A25:H25"/>
+    <x:mergeCell ref="A27:H27"/>
+    <x:mergeCell ref="A28:H30"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -28677,7 +28742,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -28721,7 +28786,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -28764,7 +28829,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -28807,7 +28872,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -28851,7 +28916,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -28879,7 +28944,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -28907,7 +28972,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -28975,7 +29040,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -29010,7 +29075,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -29045,7 +29110,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -29080,7 +29145,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -29107,7 +29172,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -29134,7 +29199,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -29162,7 +29227,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -29190,7 +29255,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -29218,7 +29283,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -29315,7 +29380,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R839c2d5584964455"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e7be2de4f5f4fd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29575,7 +29640,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -29619,7 +29684,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -29663,7 +29728,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -29707,7 +29772,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -29734,7 +29799,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -29761,7 +29826,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -29796,7 +29861,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -29831,7 +29896,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -29866,7 +29931,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -29900,7 +29965,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -29934,7 +29999,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -29962,7 +30027,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -29990,7 +30055,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -30018,7 +30083,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -30139,7 +30204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5371ee3bd3644bcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3397b227919648c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30356,7 +30421,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -30400,7 +30465,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -30444,7 +30509,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -30488,7 +30553,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -30531,7 +30596,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -30558,7 +30623,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -30586,7 +30651,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -30621,7 +30686,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -30656,7 +30721,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -30690,7 +30755,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -30724,7 +30789,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -30759,7 +30824,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -30787,7 +30852,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -30932,7 +30997,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd35b636f1a3c441a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c553dc92bcc40ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31150,7 +31215,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -31194,7 +31259,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -31237,7 +31302,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -31280,7 +31345,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -31324,7 +31389,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -31352,7 +31417,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -31380,7 +31445,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -31414,7 +31479,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -31448,7 +31513,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -31483,7 +31548,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -31518,7 +31583,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -31553,7 +31618,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -31580,7 +31645,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -31607,7 +31672,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -31635,7 +31700,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -31663,7 +31728,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -31691,7 +31756,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H26" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="23" customHeight="1">
@@ -31718,7 +31783,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H27" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="23" customHeight="1">
@@ -31803,7 +31868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a77ddaf73746ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88b763b9f6c145b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32021,7 +32086,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -32064,7 +32129,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -32107,7 +32172,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -32151,7 +32216,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -32195,7 +32260,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -32223,7 +32288,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -32250,7 +32315,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -32284,7 +32349,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -32319,7 +32384,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -32354,7 +32419,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -32389,7 +32454,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -32423,7 +32488,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -32450,7 +32515,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -32478,7 +32543,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -32506,7 +32571,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H24" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="23" customHeight="1">
@@ -32534,7 +32599,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H25" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="23" customHeight="1">
@@ -32643,7 +32708,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4897ecca508f4efe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc85d1e82f9aa4126"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32860,7 +32925,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="262" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J10" s="266" t="str">
         <x:f>'Settings'!$A$10</x:f>
@@ -32904,7 +32969,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J11" s="269" t="str">
         <x:f>'Settings'!$A$11</x:f>
@@ -32948,7 +33013,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J12" s="269" t="str">
         <x:f>'Settings'!$A$12</x:f>
@@ -32992,7 +33057,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J13" s="272" t="str">
         <x:f>'Settings'!$A$13</x:f>
@@ -33035,7 +33100,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H14" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23" customHeight="1">
@@ -33062,7 +33127,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23" customHeight="1">
@@ -33090,7 +33155,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
         <x:v>Daily tracking notes</x:v>
@@ -33125,7 +33190,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H17" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J17" s="290" t="str">
         <x:v>Product labels and goals come from Settings.</x:v>
@@ -33160,7 +33225,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H18" s="263" t="str">
-        <x:v>Follow-up requested for a later date.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
       <x:c r="J18" s="293" t="str">
         <x:v>Points use the selected product's fictional point value.</x:v>
@@ -33194,7 +33259,7 @@
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="H19" s="263" t="str">
-        <x:v>No change was made during the interaction.</x:v>
+        <x:v>Follow-up requested for a later date.</x:v>
       </x:c>
       <x:c r="J19" s="293" t="str">
         <x:v>Goal status compares completed units with the daily goal.</x:v>
@@ -33228,7 +33293,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H20" s="263" t="str">
-        <x:v>Confirmed the information provided.</x:v>
+        <x:v>No selection made; no follow-up needed.</x:v>
       </x:c>
       <x:c r="J20" s="296" t="str">
         <x:v>Replace or add only fictional demonstration rows.</x:v>
@@ -33263,7 +33328,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H21" s="263" t="str">
-        <x:v>Added a fictional reminder for follow-up.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23" customHeight="1">
@@ -33291,7 +33356,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H22" s="263" t="str">
-        <x:v>Answered the question and recorded the result.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="23" customHeight="1">
@@ -33319,7 +33384,7 @@
         <x:v>No</x:v>
       </x:c>
       <x:c r="H23" s="263" t="str">
-        <x:v>Reviewed the fictional options and next steps.</x:v>
+        <x:v>Completed the fictional selection.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="23" customHeight="1">
@@ -33452,7 +33517,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2b5f8c6a6734303"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf8dca88a734ea0"/>
   </x:tableParts>
 </x:worksheet>
 </file>